--- a/output/pdf_financials_xlsx/CCCM.xlsx
+++ b/output/pdf_financials_xlsx/CCCM.xlsx
@@ -1054,37 +1054,37 @@
         <v>-0.939184</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.739546</v>
+        <v>-0.739546</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.867768</v>
+        <v>-0.867768</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.372318</v>
+        <v>-1.372318</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.727971</v>
+        <v>-1.727971</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.271145</v>
+        <v>-2.271145</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.762323</v>
+        <v>-0.762323</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5.527468</v>
+        <v>-5.527468</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3.818961</v>
+        <v>-3.818961</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.927272</v>
+        <v>-0.927272</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.292591</v>
+        <v>-2.292591</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.90213</v>
+        <v>-2.90213</v>
       </c>
     </row>
     <row r="17">
@@ -1274,37 +1274,37 @@
         <v>-0.939184</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.739546</v>
+        <v>-0.739546</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.867768</v>
+        <v>-0.867768</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.372318</v>
+        <v>-1.372318</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.727971</v>
+        <v>-1.727971</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.271145</v>
+        <v>-2.271145</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.762323</v>
+        <v>-0.762323</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.527468</v>
+        <v>-5.527468</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.818961</v>
+        <v>-3.818961</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.927272</v>
+        <v>-0.927272</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.292591</v>
+        <v>-2.292591</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.90213</v>
+        <v>-2.90213</v>
       </c>
     </row>
     <row r="21">
@@ -1403,37 +1403,37 @@
         <v>-0.939184</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.739546</v>
+        <v>-0.739546</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.867768</v>
+        <v>-0.867768</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.372318</v>
+        <v>-1.372318</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.727971</v>
+        <v>-1.727971</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.271145</v>
+        <v>-2.271145</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.762323</v>
+        <v>-0.762323</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>5.527468</v>
+        <v>-5.527468</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.818961</v>
+        <v>-3.818961</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.927272</v>
+        <v>-0.927272</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.292591</v>
+        <v>-2.292591</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.90213</v>
+        <v>-2.90213</v>
       </c>
     </row>
     <row r="24">
@@ -1532,7 +1532,7 @@
         <v>31.306133</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>36.9773</v>
+        <v>-36.9773</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>68.6159</v>
+        <v>-68.6159</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>42.4329</v>
+        <v>-42.4329</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>46.3636</v>
+        <v>-46.3636</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>57.314775</v>
+        <v>-57.314775</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>96.737667</v>
+        <v>-96.737667</v>
       </c>
     </row>
     <row r="27">
@@ -1585,37 +1585,37 @@
         <v>-0.939184</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.739546</v>
+        <v>-0.739546</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.867768</v>
+        <v>-0.867768</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.372318</v>
+        <v>-1.372318</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.727971</v>
+        <v>-1.727971</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.271145</v>
+        <v>-2.271145</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.762323</v>
+        <v>-0.762323</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.527468</v>
+        <v>-5.527468</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>3.818961</v>
+        <v>-3.818961</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.927272</v>
+        <v>-0.927272</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.292591</v>
+        <v>-2.292591</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.90213</v>
+        <v>-2.90213</v>
       </c>
     </row>
     <row r="28">
@@ -1671,37 +1671,37 @@
         <v>-0.939184</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.739546</v>
+        <v>-0.739546</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.867768</v>
+        <v>-0.867768</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.372318</v>
+        <v>-1.372318</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.727971</v>
+        <v>-1.727971</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.271145</v>
+        <v>-2.271145</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.762323</v>
+        <v>-0.762323</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.527468</v>
+        <v>-5.527468</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.818961</v>
+        <v>-3.818961</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.927272</v>
+        <v>-0.927272</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.292591</v>
+        <v>-2.292591</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.90213</v>
+        <v>-2.90213</v>
       </c>
     </row>
     <row r="30">
@@ -1781,37 +1781,37 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -19787,13 +19787,13 @@
         </is>
       </c>
       <c r="N187" s="5" t="n">
-        <v>0.927272</v>
+        <v>-0.927272</v>
       </c>
       <c r="O187" s="5" t="n">
-        <v>2.292591</v>
+        <v>-2.292591</v>
       </c>
       <c r="P187" s="5" t="n">
-        <v>2.90213</v>
+        <v>-2.90213</v>
       </c>
     </row>
     <row r="188">
@@ -19940,10 +19940,10 @@
         </is>
       </c>
       <c r="O189" s="5" t="n">
-        <v>3.265699</v>
+        <v>-3.265699</v>
       </c>
       <c r="P189" s="5" t="n">
-        <v>1.251664</v>
+        <v>-1.251664</v>
       </c>
     </row>
     <row r="190">
@@ -20873,13 +20873,13 @@
         <v>-0.939184</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>0.739546</v>
+        <v>-0.739546</v>
       </c>
       <c r="G203" s="5" t="n">
-        <v>0.867768</v>
+        <v>-0.867768</v>
       </c>
       <c r="H203" s="5" t="n">
-        <v>1.372318</v>
+        <v>-1.372318</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -20902,10 +20902,10 @@
         </is>
       </c>
       <c r="M203" s="5" t="n">
-        <v>3.818961</v>
+        <v>-3.818961</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>0.927272</v>
+        <v>-0.927272</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -21521,22 +21521,22 @@
         </is>
       </c>
       <c r="H212" s="5" t="n">
-        <v>1.372318</v>
+        <v>-1.372318</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>1.727971</v>
+        <v>-1.727971</v>
       </c>
       <c r="J212" s="5" t="n">
-        <v>2.271145</v>
+        <v>-2.271145</v>
       </c>
       <c r="K212" s="5" t="n">
-        <v>0.762323</v>
+        <v>-0.762323</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>5.527468</v>
+        <v>-5.527468</v>
       </c>
       <c r="M212" s="5" t="n">
-        <v>3.818961</v>
+        <v>-3.818961</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
@@ -21579,28 +21579,28 @@
         <v>-1.031209</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>0.445279</v>
+        <v>-0.445279</v>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1.084685</v>
+        <v>-1.084685</v>
       </c>
       <c r="H213" s="5" t="n">
-        <v>1.510003</v>
+        <v>-1.510003</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>1.82466</v>
+        <v>-1.82466</v>
       </c>
       <c r="J213" s="5" t="n">
-        <v>2.168594</v>
+        <v>-2.168594</v>
       </c>
       <c r="K213" s="5" t="n">
-        <v>1.204564</v>
+        <v>-1.204564</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>6.067138</v>
+        <v>-6.067138</v>
       </c>
       <c r="M213" s="5" t="n">
-        <v>2.422402</v>
+        <v>-2.422402</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CCCM.xlsx
+++ b/output/pdf_financials_xlsx/CCCM.xlsx
@@ -823,10 +823,10 @@
         <v>2.505714</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.683399</v>
+        <v>2.334389</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.72662</v>
+        <v>3.267871</v>
       </c>
     </row>
     <row r="11">
@@ -866,10 +866,10 @@
         <v>-2.505714</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.683399</v>
+        <v>-2.334389</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.72662</v>
+        <v>-3.267871</v>
       </c>
     </row>
     <row r="12">
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000202</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000546</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000231</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002616</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010055</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007981</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008155000000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022821</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07561900000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.083331</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.13499</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.228207</v>
       </c>
     </row>
     <row r="13">
@@ -1582,40 +1582,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.939184</v>
+        <v>-0.938982</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.739546</v>
+        <v>-0.739</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.867768</v>
+        <v>-0.867537</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.372318</v>
+        <v>-1.369702</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.727971</v>
+        <v>-1.717916</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.271145</v>
+        <v>-2.263164</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.762323</v>
+        <v>-0.7541679999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.527468</v>
+        <v>-5.504647</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.818961</v>
+        <v>-3.743342</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.927272</v>
+        <v>-0.8439410000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.292591</v>
+        <v>-2.157601</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.90213</v>
+        <v>-2.673923</v>
       </c>
     </row>
     <row r="28">
@@ -1668,40 +1668,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.939184</v>
+        <v>-0.938982</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.739546</v>
+        <v>-0.739</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.867768</v>
+        <v>-0.867537</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.372318</v>
+        <v>-1.369702</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.727971</v>
+        <v>-1.717916</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.271145</v>
+        <v>-2.263164</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.762323</v>
+        <v>-0.7541679999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.527468</v>
+        <v>-5.504647</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.818961</v>
+        <v>-3.743342</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.927272</v>
+        <v>-0.8439410000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.292591</v>
+        <v>-2.157601</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.90213</v>
+        <v>-2.673923</v>
       </c>
     </row>
     <row r="30">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E200" s="5" t="n">
@@ -21286,7 +21286,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -21938,7 +21938,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">

--- a/output/pdf_financials_xlsx/CCCM.xlsx
+++ b/output/pdf_financials_xlsx/CCCM.xlsx
@@ -3236,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.423506</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.157889</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
@@ -3365,10 +3365,10 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.05864</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.167319</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
@@ -5256,22 +5256,22 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.02709</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.060869</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015434</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.058267</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.027952</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002041</v>
       </c>
     </row>
     <row r="112">
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.816381</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.02697</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.271211</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.02709</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.060869</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015434</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.058267</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.027952</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002041</v>
       </c>
     </row>
     <row r="135">
@@ -6312,22 +6312,22 @@
         <v>-1.032066</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.658218</v>
+        <v>-1.685308</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-2.065991</v>
+        <v>-2.12686</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-3.78957</v>
+        <v>-3.805004</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-2.600451</v>
+        <v>-2.658718</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-2.3502</v>
+        <v>-2.378152</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-2.406237</v>
+        <v>-2.408278</v>
       </c>
     </row>
   </sheetData>
@@ -11480,7 +11480,11 @@
           <t>Purchase of equipment (note 5)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -12580,7 +12584,11 @@
           <t>Proceeds from sale of marketable securities (note 6)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -12726,7 +12734,11 @@
           <t>Purchase of equipment (note 7)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
